--- a/5/search/combined_defense_results/best_strategy_details.xlsx
+++ b/5/search/combined_defense_results/best_strategy_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>278.2</v>
+        <v>292.8</v>
       </c>
       <c r="C5" t="n">
-        <v>139.5</v>
+        <v>127.6</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -580,21 +580,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>131.3</v>
+        <v>125.8</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>21.8</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -603,82 +603,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY3</t>
+          <t>FY4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.59999999999999</v>
+        <v>295.4</v>
       </c>
       <c r="C7" t="n">
-        <v>131.3</v>
+        <v>105.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FY4</t>
+          <t>FY5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>122.7</v>
+        <v>135.4</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FY5</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>116.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>138</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/combined_defense_results/best_strategy_details.xlsx
+++ b/5/search/combined_defense_results/best_strategy_details.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>292.8</v>
+        <v>278.2</v>
       </c>
       <c r="C5" t="n">
-        <v>127.6</v>
+        <v>139.4</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -580,24 +580,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82</v>
+        <v>82.3</v>
       </c>
       <c r="C6" t="n">
-        <v>125.8</v>
+        <v>135.4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>21.8</v>
+        <v>19.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
